--- a/data/gravel/Seeker Steel Gravel 2025.xlsx
+++ b/data/gravel/Seeker Steel Gravel 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F663DE1-9656-BC4C-B3E3-927A87C92F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6072A5E-3A7E-3741-84AE-4CE46281A8F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12600" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t>brand</t>
   </si>
@@ -345,6 +345,9 @@
   </si>
   <si>
     <t>not spec'd</t>
+  </si>
+  <si>
+    <t>Olympia, Washington, USA</t>
   </si>
 </sst>
 </file>
@@ -1358,6 +1361,9 @@
       <c r="A57" t="s">
         <v>44</v>
       </c>
+      <c r="B57">
+        <v>27.2</v>
+      </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
@@ -1486,6 +1492,9 @@
     <row r="79" spans="1:3">
       <c r="A79" s="1" t="s">
         <v>75</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
